--- a/GC-LLP-INTAKE-TEMPLATE.xlsx
+++ b/GC-LLP-INTAKE-TEMPLATE.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\gc-app\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GC BUILD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CCD7D16D-F851-4E27-BA92-1F6A639420D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C598D0BE-C9F0-4122-89AE-E0D3902C2D0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38310" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="500" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -728,18 +728,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="E6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000009000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t>PENDING - coordinates not supplied.</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="F6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000C000000}">
       <text>
         <r>
@@ -788,7 +776,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000A000000}">
+    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000009000000}">
       <text>
         <r>
           <rPr>
@@ -1442,18 +1430,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-00000A000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t>Operator share mirrored from Seaside Confluence platform convention.</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="F7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-00000C000000}">
       <text>
         <r>
@@ -2027,7 +2003,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="368">
   <si>
     <t>Getaway Collective · LLP Intake Template</t>
   </si>
@@ -3125,6 +3101,12 @@
   </si>
   <si>
     <t>.3 acres · dual frontage</t>
+  </si>
+  <si>
+    <t>12°23'25.8"N 75°49'15.2"E</t>
+  </si>
+  <si>
+    <t>13°24'40.5"N 77°49'26.9"E</t>
   </si>
 </sst>
 </file>
@@ -4482,7 +4464,7 @@
       </c>
       <c r="D6" s="5" t="str">
         <f>IF('5 Operating &amp; waterfall'!E6="","",IF(AND('5 Operating &amp; waterfall'!E6&gt;0,'5 Operating &amp; waterfall'!F6&gt;0,'5 Operating &amp; waterfall'!G6&gt;0,'5 Operating &amp; waterfall'!H6&gt;0,'5 Operating &amp; waterfall'!I6&gt;0,'5 Operating &amp; waterfall'!E6+'5 Operating &amp; waterfall'!F6+'5 Operating &amp; waterfall'!G6+'5 Operating &amp; waterfall'!H6+'5 Operating &amp; waterfall'!I6&lt;10000),"PASS","FAIL"))</f>
-        <v/>
+        <v>PASS</v>
       </c>
       <c r="E6" s="5" t="str">
         <f>IF('5 Operating &amp; waterfall'!J6="","",IF('5 Operating &amp; waterfall'!J6&gt;0,"PASS","FAIL"))</f>
@@ -6697,7 +6679,9 @@
       <c r="D6" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E6" s="7"/>
+      <c r="E6" s="7" t="s">
+        <v>367</v>
+      </c>
       <c r="F6" s="7"/>
       <c r="G6" s="7" t="s">
         <v>77</v>
@@ -6729,7 +6713,9 @@
       <c r="D7" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="E7" s="7"/>
+      <c r="E7" s="7" t="s">
+        <v>366</v>
+      </c>
       <c r="F7" s="7"/>
       <c r="G7" s="7" t="s">
         <v>82</v>
@@ -7676,8 +7662,7 @@
         <v>55000000</v>
       </c>
       <c r="L6" s="15">
-        <f>+I6/M6</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M6" s="13">
         <f t="shared" ref="M6:M7" si="1">+G6/(B6/100)</f>
@@ -7687,7 +7672,7 @@
         <v>0</v>
       </c>
       <c r="O6" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P6" s="9">
         <v>50000</v>
@@ -8288,14 +8273,24 @@
         <f>IFERROR(IF(B6="","",INDEX('2 Property'!$H$5:$H$25,MATCH(A6,'2 Property'!$A$5:$A$25,0))*365*(C6/10000)*B6),"")</f>
         <v>13140000</v>
       </c>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="15">
-        <f t="shared" si="0"/>
-        <v>10000</v>
+      <c r="E6" s="14">
+        <v>4000</v>
+      </c>
+      <c r="F6" s="12">
+        <v>1500</v>
+      </c>
+      <c r="G6" s="12">
+        <v>250</v>
+      </c>
+      <c r="H6" s="12">
+        <v>250</v>
+      </c>
+      <c r="I6" s="12">
+        <v>2308</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" ref="J6" si="1">IF(B6="","",10000-E6-F6-G6-H6-I6)</f>
+        <v>1692</v>
       </c>
       <c r="K6" s="10"/>
       <c r="L6" s="8"/>
@@ -8314,8 +8309,8 @@
         <f>IFERROR(IF(B7="","",INDEX('2 Property'!$H$5:$H$25,MATCH(A7,'2 Property'!$A$5:$A$25,0))*365*(C7/10000)*B7),"")</f>
         <v>48180000.000000007</v>
       </c>
-      <c r="E7" s="12">
-        <v>3500</v>
+      <c r="E7" s="14">
+        <v>4000</v>
       </c>
       <c r="F7" s="12">
         <v>1500</v>
@@ -8331,7 +8326,7 @@
       </c>
       <c r="J7" s="15">
         <f t="shared" si="0"/>
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="K7" s="9">
         <v>8700000</v>
